--- a/Översikt ENKÖPING.xlsx
+++ b/Översikt ENKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44697</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45831</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>44910</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>46150</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46238</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45511</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>46269</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>44552</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>44575</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45104</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>46233</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>45104</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44530</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>46255</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>46255</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>46265</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>44552</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44873</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>45215</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45226</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>45631</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>46170</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>45825</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>45191</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>46070</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>45190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45762</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>44526</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>45697</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>44935</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>45480</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>45994</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>46008</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>44735</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>44910</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>46044</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>44722</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>45775</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>46272</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>46265</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>46279</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>46194</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45037</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45177</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>46203</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>44475</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>44477</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>44501</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>44497</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>44482</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44473</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>44680</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>44622</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44622</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44851</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>44687</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>44819</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>44587</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>44566</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44575</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44858</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>44655</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>44753</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44753</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>44810</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>44580</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44809</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>44575</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>44526</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>44532</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>44482</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>44497</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>44657</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>44768</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>44575</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>44664</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44664</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44694</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>44482</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>44728</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>44679</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>44490</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>44728</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>44482</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>44867</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>45758</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>45588</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>44862</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>44879</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>45098</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>44664</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>44859</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>45330</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>45565</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>45720</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>45762</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>44707</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>45044</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>44964</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>45048</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>45007</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>44664</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>44844</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>45561</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>44482</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>44831</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>45476</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>45539</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>45191</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>45503</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>45267</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>44910</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>44623</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>45274</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>44978</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         <v>45572</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>45033</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>45239</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>44600</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>45596</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>44753</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>45097</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11373,7 +11373,7 @@
         <v>45600</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         <v>45261</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>45733</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>45428</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>45629</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         <v>45219</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>44838</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>44603</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>45715</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>45337</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>45523</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>45033</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>45196</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>45181</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>44473</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>45617</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>45202</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>44963</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45264</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>44568</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>44477</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>45181</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>45358</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>45825</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>45183</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>44844</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>45569</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         <v>44531</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>44547</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>44795</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>44575</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>45670</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>45569</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>45225</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>45085</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>45061</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>45223</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>45565</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>45405</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>45040</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>45903</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>45877</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>44853</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>45789</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>45209</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>45520</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>45429</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>45923</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>44623</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>45393</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>45820</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>45926</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>44824</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>45083</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>45679</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>45889</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>45733</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>45937</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>45909</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>45160</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>45069</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>45947</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>45527</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>45131</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>45804</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>44477</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         <v>45589</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>44872</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>46150</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>45677</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>44907</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>44979</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>45733</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>45636</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>46154</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>45966</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>45083</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>45044</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>45979</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>45979</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>44941</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>44502</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>45993</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>44532</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>46162</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>46052</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>46052</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45021</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45994</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>44941</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>44941</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>45994</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>45999</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>45434</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>45999</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>46001</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>45947</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>46167</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>45628</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>44941</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>46003</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>45511</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>46167</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>45628</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>46009</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>46007</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>46007</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>45701</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>46007</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>44761</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45099</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>45457</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>45999</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>46025</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>46030</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>45677</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>46036</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>46174</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>44893</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>45553</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45001</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>44901</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>44907</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>44525</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>44789</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>46050</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>45369</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>46052</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>44525</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>46052</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20873,7 +20873,7 @@
         <v>46052</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>45215</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>46057</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>46057</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>46177</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>44991</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>46177</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>44482</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>44482</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>45350</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45350</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>44980</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>46064</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>44676</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>46071</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>46071</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>46071</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>46070</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45117</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>45744</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>45609</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>45230</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>45554</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>44482</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>46090</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>45224</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>46052</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>46092</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>44763</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>46096</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>45008</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23141,7 +23141,7 @@
         <v>46099</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>46099</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>46099</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23360,7 +23360,7 @@
         <v>46099</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         <v>45607</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>44575</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>46099</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>46104</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23725,7 +23725,7 @@
         <v>46106</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>45596</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>45631</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23944,7 +23944,7 @@
         <v>45362</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>45477</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24090,7 +24090,7 @@
         <v>44531</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>46120</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44869</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>46120</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
         <v>44824</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>46007</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>44676</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24601,7 +24601,7 @@
         <v>44827</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24674,7 +24674,7 @@
         <v>45707</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24747,7 +24747,7 @@
         <v>46070</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24820,7 +24820,7 @@
         <v>46128</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>46245</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>46128</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>46128</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>46127</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25185,7 +25185,7 @@
         <v>45453</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>46127</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>45489</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>45139</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>45629</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>44753</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>44753</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>44839</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>44915</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>45164</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>45055</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>44609</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>45554</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>45155</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26212,7 +26212,7 @@
         <v>44875</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26285,7 +26285,7 @@
         <v>44735</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26363,7 +26363,7 @@
         <v>45323</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26436,7 +26436,7 @@
         <v>45448</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26509,7 +26509,7 @@
         <v>45099</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>45679</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26655,7 +26655,7 @@
         <v>46049</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26728,7 +26728,7 @@
         <v>45306</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>46209</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26879,7 +26879,7 @@
         <v>45181</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>44966</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>46211</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>46255</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>45632</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>44950</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>45764</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>46260</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>45385</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>45306</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27609,7 +27609,7 @@
         <v>46261</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27682,7 +27682,7 @@
         <v>44900</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>44508</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27828,7 +27828,7 @@
         <v>46265</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27901,7 +27901,7 @@
         <v>44693</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>44594</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28047,7 +28047,7 @@
         <v>44775</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28120,7 +28120,7 @@
         <v>45377</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28193,7 +28193,7 @@
         <v>46266</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>45638</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>45188</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>44496</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>45527</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>46269</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>46265</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         <v>46275</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>46279</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28860,7 +28860,7 @@
         <v>46279</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>45489</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>45618</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29079,7 +29079,7 @@
         <v>45741</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>45701</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>44526</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>45789</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>45789</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29444,7 +29444,7 @@
         <v>46281</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>46281</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>45790</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>45580</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>44609</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29809,7 +29809,7 @@
         <v>44557</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         <v>45526</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>45694</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>45694</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>45656</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>45727</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30247,7 +30247,7 @@
         <v>45457</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30320,7 +30320,7 @@
         <v>45632</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30393,7 +30393,7 @@
         <v>45804</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30466,7 +30466,7 @@
         <v>45804</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>45804</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30612,7 +30612,7 @@
         <v>45527</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30685,7 +30685,7 @@
         <v>45548</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>45709</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>45820</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>45831</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>45835</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>45748</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31123,7 +31123,7 @@
         <v>45764</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>45631</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31269,7 +31269,7 @@
         <v>45596</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>45758</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>45782</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>45868</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31561,7 +31561,7 @@
         <v>45870</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>45596</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>44438</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31780,7 +31780,7 @@
         <v>45692</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>

--- a/Översikt ENKÖPING.xlsx
+++ b/Översikt ENKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44697</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45831</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>44910</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>46150</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46238</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45511</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>46269</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>44552</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>45104</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>46233</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44575</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>45104</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44530</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>46255</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>46255</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>46265</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>44552</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44873</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>45226</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45215</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>45631</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>46170</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>45190</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>46070</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>45825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>45191</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45762</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>44526</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>45037</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>44910</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>46044</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>44722</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>45480</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>45994</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>46008</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>44935</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>45697</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>45775</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44735</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>46272</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>46265</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         <v>46279</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>46194</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45177</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>46203</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>44475</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>44477</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>44501</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>44497</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>44482</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44473</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>44680</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>44622</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44622</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44851</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>44687</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>44819</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>44587</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>44566</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44575</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44858</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>44655</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>44753</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44810</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>44753</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>44580</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44809</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>44575</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>44526</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>44532</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>44482</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>44497</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>44657</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>44768</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>44575</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>44664</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44664</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44694</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>44482</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>44728</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>44679</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>44490</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>44728</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>44482</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>45330</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>45323</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>45720</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>44867</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>44482</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>45083</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>44761</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>45181</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>45434</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>45733</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>44872</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>45385</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>44824</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>45457</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>45202</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>44839</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>44910</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>44844</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>44893</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>45489</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>45306</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>45694</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>44609</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>45999</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>45526</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>44531</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>45656</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>46025</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>45694</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>45503</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>46030</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         <v>44941</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>45580</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>44477</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>45727</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>44557</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>45477</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>46036</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>44531</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>45632</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>45476</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11597,7 +11597,7 @@
         <v>45448</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>44853</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
         <v>45903</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>45362</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11889,7 +11889,7 @@
         <v>46050</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>46052</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>46052</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>46052</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         <v>45457</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>45789</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         <v>46057</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>45181</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>45804</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>46057</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>45008</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>46064</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>45804</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>46070</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>45804</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>45923</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>46071</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>46071</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>44623</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>45926</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>46071</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>45527</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>44941</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>45523</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>44964</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>46090</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>45889</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>46052</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>45909</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>46092</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>45937</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14152,7 +14152,7 @@
         <v>46096</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>46099</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>46099</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>46099</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>46099</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>46099</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>44707</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>44753</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>46104</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>45947</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>45804</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>46106</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>45629</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         <v>46120</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>45677</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>46120</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>45966</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>46127</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>44676</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         <v>44824</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         <v>46127</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>46007</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         <v>45083</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>46128</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>46128</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>46070</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>45979</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>45636</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         <v>45979</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>45679</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45701</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>45993</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45994</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>45994</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>45999</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>45224</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>45999</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>45511</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>45264</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>46001</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>45055</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>44502</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>45820</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>46003</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>45548</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>46007</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>46007</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>44907</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45709</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>46007</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>44831</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>46009</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>45565</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>45715</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>45820</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>45155</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>45569</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45569</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>45196</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>45744</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>45762</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>45337</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>44525</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>45877</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>45825</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44838</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>44827</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>45831</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>44473</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>45069</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>46150</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>45085</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45188</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>44753</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>44753</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>46154</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>44879</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>45350</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45099</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>45369</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>44941</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>44941</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45835</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45007</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>46162</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>46052</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>46052</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>45748</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>45631</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>44508</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>45764</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>45596</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>45947</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>44915</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45628</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45358</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>44568</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>44991</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>45758</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>46167</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>46167</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>45099</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>45628</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>44901</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>45405</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>45782</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>44482</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>44482</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44594</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>45764</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>45429</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>46174</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>45520</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>45215</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>45868</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>46177</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>46177</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45428</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>44525</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>45870</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>45164</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>44963</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>45553</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23131,7 +23131,7 @@
         <v>44978</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>44609</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>45758</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>44664</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>45600</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>45596</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>44547</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45160</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>44603</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>45048</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>45061</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23939,7 +23939,7 @@
         <v>44477</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>44795</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>45554</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>45554</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>44532</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>45453</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>45677</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>46209</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>44789</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24601,7 +24601,7 @@
         <v>46049</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24674,7 +24674,7 @@
         <v>46211</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24747,7 +24747,7 @@
         <v>45117</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24820,7 +24820,7 @@
         <v>45638</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>44693</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>46255</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>45561</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>44676</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25185,7 +25185,7 @@
         <v>45572</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>44763</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>46260</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>45679</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>46261</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>45219</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>45225</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>45274</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>46266</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>45267</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>45261</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>46269</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>44950</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>44735</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
         <v>46265</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>46275</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26368,7 +26368,7 @@
         <v>46279</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>46279</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26514,7 +26514,7 @@
         <v>44623</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>45191</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>45631</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26733,7 +26733,7 @@
         <v>46281</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>45393</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26879,7 +26879,7 @@
         <v>45044</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>46281</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>45131</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>45539</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>44575</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>45040</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>44862</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>46287</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>46287</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>45565</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27609,7 +27609,7 @@
         <v>46287</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27682,7 +27682,7 @@
         <v>46265</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>44859</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27828,7 +27828,7 @@
         <v>44775</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27901,7 +27901,7 @@
         <v>46245</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>46289</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28047,7 +28047,7 @@
         <v>44600</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28120,7 +28120,7 @@
         <v>44482</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28193,7 +28193,7 @@
         <v>46290</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28271,7 +28271,7 @@
         <v>45589</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28344,7 +28344,7 @@
         <v>45607</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28417,7 +28417,7 @@
         <v>46290</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>46288</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>45181</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>45306</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>45033</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28792,7 +28792,7 @@
         <v>45033</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28865,7 +28865,7 @@
         <v>45609</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28938,7 +28938,7 @@
         <v>44575</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29011,7 +29011,7 @@
         <v>44966</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         <v>45209</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>44900</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>45527</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>45223</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>44496</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>45021</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29522,7 +29522,7 @@
         <v>45183</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>45239</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>45377</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>44844</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>45632</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>45139</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45629</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>45001</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>45596</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>44980</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>45097</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>45044</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>44979</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>45098</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>44664</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>45230</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>44907</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>45596</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>45733</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>44875</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>45588</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>45733</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         <v>45617</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>44869</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>45707</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>45350</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>45527</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>45741</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>45618</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>45489</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>45789</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>45789</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>45701</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>45790</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>44526</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>44438</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>45692</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>

--- a/Översikt ENKÖPING.xlsx
+++ b/Översikt ENKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44697</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45831</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>44910</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>46150</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46238</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45511</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>46269</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>44552</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>45104</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>46233</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44575</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>45104</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44530</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>46255</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>46255</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>46265</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>44552</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44873</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>45226</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45215</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>45631</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>46170</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>45190</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>46070</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>45825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>45191</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45762</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>44526</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>45037</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>44910</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>46044</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>44722</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>45480</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>45994</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>46008</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>44935</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>45697</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>45775</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44735</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>46272</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>46265</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         <v>46279</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>46194</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45177</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>46203</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>44475</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>44477</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>44501</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>44497</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>44482</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44473</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>44680</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>44622</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44622</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44851</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>44687</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>44819</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>44587</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>44566</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44575</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44858</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>44655</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>44753</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44810</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>44753</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>44580</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44809</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>44575</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>44526</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>44532</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>44482</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>44497</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>44657</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>44768</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>44575</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>44664</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44664</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44694</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>44482</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>44728</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>44679</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>44490</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>44728</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>44482</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>45330</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>45323</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>45720</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>44867</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>44482</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>45083</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>44761</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>45181</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>45434</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>45733</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>44872</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>45385</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>44824</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>45457</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>45202</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>44839</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>44910</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>44844</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>44893</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>45489</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>45306</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>45694</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>44609</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>45999</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>45526</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>44531</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>45656</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>46025</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>45694</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>45503</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>46030</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         <v>44941</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>45580</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>44477</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>45727</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>44557</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>45477</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>46036</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>44531</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>45632</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>45476</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11597,7 +11597,7 @@
         <v>45448</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>44853</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
         <v>45903</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>45362</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11889,7 +11889,7 @@
         <v>46050</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>46052</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>46052</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>46052</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         <v>45457</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>45789</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         <v>46057</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>45181</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>45804</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>46057</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>45008</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>46064</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>45804</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>46070</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>45804</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>45923</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>46071</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>46071</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>44623</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>45926</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>46071</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>45527</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>44941</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>45523</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>44964</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>46090</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>45889</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>46052</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>45909</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>46092</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>45937</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14152,7 +14152,7 @@
         <v>46096</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>46099</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>46099</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>46099</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>46099</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>46099</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>44707</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>44753</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>46104</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>45947</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>45804</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>46106</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>45629</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         <v>46120</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>45677</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>46120</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>45966</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>46127</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>44676</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         <v>44824</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         <v>46127</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>46007</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         <v>45083</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>46128</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>46128</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>46070</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>45979</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>45636</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         <v>45979</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>45679</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45701</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>45993</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45994</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>45994</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>45999</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>45224</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>45999</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>45511</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>45264</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>46001</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>45055</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>44502</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>45820</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>46003</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>45548</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>46007</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>46007</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>44907</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45709</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>46007</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>44831</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>46009</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>45565</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>45715</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>45820</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>45155</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>45569</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45569</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>45196</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>45744</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>45762</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>45337</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>44525</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>45877</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>45825</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44838</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>44827</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>45831</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>44473</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>45069</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>46150</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>45085</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45188</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>44753</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>44753</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>46154</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>44879</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>45350</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45099</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>45369</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>44941</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>44941</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45835</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45007</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>46162</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>46052</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>46052</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>45748</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>45631</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>44508</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>45764</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>45596</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>45947</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>44915</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45628</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45358</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>44568</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>44991</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>45758</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>46167</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>46167</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>45099</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>45628</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>44901</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>45405</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>45782</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>44482</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>44482</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44594</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>45764</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>45429</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>46174</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>45520</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>45215</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>45868</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>46177</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>46177</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45428</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>44525</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>45870</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>45164</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>44963</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>45553</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23131,7 +23131,7 @@
         <v>44978</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>44609</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>45758</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>44664</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>45600</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>45596</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>44547</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45160</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>44603</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>45048</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>45061</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23939,7 +23939,7 @@
         <v>44477</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>44795</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>45554</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>45554</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>44532</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>45453</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>45677</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>46209</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>44789</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24601,7 +24601,7 @@
         <v>46049</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24674,7 +24674,7 @@
         <v>46211</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24747,7 +24747,7 @@
         <v>45117</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24820,7 +24820,7 @@
         <v>45638</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>44693</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>46255</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>45561</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>44676</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25185,7 +25185,7 @@
         <v>45572</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>44763</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>46260</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>45679</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>46261</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>45219</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>45225</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>45274</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>46266</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>45267</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>45261</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>46269</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>44950</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>44735</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
         <v>46265</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>46275</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26368,7 +26368,7 @@
         <v>46279</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>46279</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26514,7 +26514,7 @@
         <v>44623</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>45191</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>45631</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26733,7 +26733,7 @@
         <v>46281</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>45393</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26879,7 +26879,7 @@
         <v>45044</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>46281</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>45131</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>45539</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>44575</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>45040</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>44862</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>46287</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>46287</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>45565</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27609,7 +27609,7 @@
         <v>46287</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27682,7 +27682,7 @@
         <v>46265</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>44859</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27828,7 +27828,7 @@
         <v>44775</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27901,7 +27901,7 @@
         <v>46245</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>46289</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28047,7 +28047,7 @@
         <v>44600</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28120,7 +28120,7 @@
         <v>44482</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28193,7 +28193,7 @@
         <v>46290</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28271,7 +28271,7 @@
         <v>45589</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28344,7 +28344,7 @@
         <v>45607</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28417,7 +28417,7 @@
         <v>46290</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>46288</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>45181</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>45306</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>45033</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28792,7 +28792,7 @@
         <v>45033</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28865,7 +28865,7 @@
         <v>45609</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28938,7 +28938,7 @@
         <v>44575</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29011,7 +29011,7 @@
         <v>44966</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         <v>45209</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>44900</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>45527</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>45223</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>44496</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>45021</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29522,7 +29522,7 @@
         <v>45183</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>45239</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>45377</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>44844</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>45632</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>45139</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45629</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>45001</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>45596</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>44980</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>45097</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>45044</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>44979</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>45098</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>44664</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>45230</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>44907</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>45596</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>45733</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>44875</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>45588</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>45733</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         <v>45617</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>44869</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>45707</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>45350</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>45527</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>45741</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>45618</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>45489</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>45789</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>45789</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>45701</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>45790</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>44526</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>44438</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>45692</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>

--- a/Översikt ENKÖPING.xlsx
+++ b/Översikt ENKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44697</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45831</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>44910</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>46150</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46238</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45511</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>46269</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>44552</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>44575</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>46233</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>45104</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>45104</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44530</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>46265</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>46255</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>46255</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>44552</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44873</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>45215</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45226</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>45631</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>46170</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>46070</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>45825</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>45191</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>45190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45762</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>44526</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>45697</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>46008</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>45037</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44935</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>45994</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>45480</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>44735</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>44910</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>46272</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>46265</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>46279</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>46194</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>44722</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         <v>45775</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45177</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>46203</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>44475</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>44477</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>44501</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44497</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>44482</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>44473</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>44622</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>44622</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>44680</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>44851</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>44687</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>44819</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>44587</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>44566</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>44575</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44858</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>44655</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>44858</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44753</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>44810</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44753</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44580</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>44809</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>44575</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>44526</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44532</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>44482</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>44497</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>44657</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>44768</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>44575</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>44664</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>44664</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>44694</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>44482</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>44728</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>44679</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>44490</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>44728</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>44482</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>45758</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>44862</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>45007</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>45588</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>44664</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45098</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>44867</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>44879</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>44859</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>45330</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45720</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>45762</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44964</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>44707</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>45044</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45565</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>45701</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>44526</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>45789</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>45476</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>45789</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>45048</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>44664</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>44482</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>46003</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>44844</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>45561</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>44477</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>44831</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>46009</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>46007</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>46007</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>46007</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>45539</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>45191</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>44531</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>45503</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>45999</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>46025</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>45267</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>46030</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>44910</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>45790</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45903</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>44853</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>46036</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>45789</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>44623</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>45580</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>44609</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>44557</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>45526</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>45694</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>45694</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>45572</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>45656</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>44978</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>45727</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>45457</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>45274</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>46050</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>45632</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>45804</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>45804</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>45804</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>45033</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>45239</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>46052</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>46052</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45923</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>46052</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>46057</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>46057</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>45926</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>44600</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>45527</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>46064</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>45889</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>45937</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>46071</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>46071</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>45909</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>46071</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>46070</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45596</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>44753</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>45947</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>45097</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>45261</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>45804</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>45600</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45428</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>46090</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>45629</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>45219</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>45733</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>45677</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>46052</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>46092</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>44838</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>45966</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>44603</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>45715</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>45337</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>45523</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>46096</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>46099</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>46099</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>46099</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>46099</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>46099</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>46104</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>46106</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>45033</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>45548</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>45709</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>45979</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>45820</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>45979</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>45181</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45196</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44473</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>45617</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>45202</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>46120</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>46120</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44963</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>45993</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>44568</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>45181</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>44824</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>46007</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>44676</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>45358</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>45994</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>46070</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>46128</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>45999</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>46128</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>46127</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>45999</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>46001</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45183</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>44844</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>46127</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>44547</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>45831</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>44795</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>44575</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>45835</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>45225</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>45085</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>45223</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>45748</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45405</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>45040</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>45264</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>45764</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45631</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>45596</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>45825</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>45569</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45209</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>45520</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>45758</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>45429</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>45569</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>45565</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>44623</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>45393</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>44824</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>45877</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>45782</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45083</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>45679</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>45733</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45160</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>45868</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>45069</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         <v>45820</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>45527</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>45131</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>44477</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>45589</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>44872</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>45870</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>44907</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>46150</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>44979</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>46154</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>45733</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>45636</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>45083</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
         <v>46162</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>45044</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>46052</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>46052</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>45947</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>46167</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>45628</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>46167</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>45628</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>45596</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44941</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>46174</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>44502</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>44532</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>45215</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>45061</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>46177</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>46177</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>45021</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         <v>44941</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44941</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>45434</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24190,7 +24190,7 @@
         <v>44941</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>45511</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24336,7 +24336,7 @@
         <v>45701</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24409,7 +24409,7 @@
         <v>44761</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24482,7 +24482,7 @@
         <v>45099</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>45457</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>45677</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>46049</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>46209</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>44893</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>45553</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>46211</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>45001</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>44901</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>44907</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>44525</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>44789</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>46260</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>45369</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>46261</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>44525</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>44991</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25801,7 +25801,7 @@
         <v>44482</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
         <v>44482</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>45350</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26020,7 +26020,7 @@
         <v>45350</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>44980</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26166,7 +26166,7 @@
         <v>44676</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>46266</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         <v>45117</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>45744</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>46269</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>45609</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>45230</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26687,7 +26687,7 @@
         <v>46265</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>45554</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>46275</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>46279</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>46279</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27057,7 +27057,7 @@
         <v>44482</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>46281</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27203,7 +27203,7 @@
         <v>46281</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>45224</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44763</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>45008</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27495,7 +27495,7 @@
         <v>45607</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>44575</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>46287</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27714,7 +27714,7 @@
         <v>46287</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>46287</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>45596</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27933,7 +27933,7 @@
         <v>45631</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>45362</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>46265</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>45477</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>44531</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>46245</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>44869</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>46289</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>44827</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>45707</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>46290</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>45453</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>46290</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>45489</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>45139</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>46288</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45629</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>44753</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>44753</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>44839</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>44915</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>46294</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>45164</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>45055</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>44609</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29773,7 +29773,7 @@
         <v>45554</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>45155</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44875</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>44735</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>45323</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30143,7 +30143,7 @@
         <v>45448</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30216,7 +30216,7 @@
         <v>46255</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>45099</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30362,7 +30362,7 @@
         <v>45679</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30435,7 +30435,7 @@
         <v>45306</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30513,7 +30513,7 @@
         <v>45181</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>44966</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30659,7 +30659,7 @@
         <v>45632</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44950</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45764</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30878,7 +30878,7 @@
         <v>45385</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>45306</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>44900</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31097,7 +31097,7 @@
         <v>44508</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>44693</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>44594</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>44775</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>45377</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31462,7 +31462,7 @@
         <v>45638</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>45188</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>44496</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>45527</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>45489</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31827,7 +31827,7 @@
         <v>45618</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31900,7 +31900,7 @@
         <v>45741</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31973,7 +31973,7 @@
         <v>44438</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>45692</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>

--- a/Översikt ENKÖPING.xlsx
+++ b/Översikt ENKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44697</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45831</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>44910</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>46150</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46238</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45511</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>46269</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>44552</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>44575</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>46233</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>45104</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>45104</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44530</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>46265</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>46255</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>46255</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>44552</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44873</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>45215</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45226</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>45631</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>46170</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>46070</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>45825</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>45191</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>45190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45762</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>44526</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>45697</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>46008</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>45037</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44935</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>45994</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>45480</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>44735</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>44910</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>46272</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>46265</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>46279</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>46194</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>44722</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         <v>45775</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45177</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>46203</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>44475</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>44477</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>44501</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44497</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>44482</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>44473</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>44622</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>44622</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>44680</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>44851</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>44687</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>44819</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>44587</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>44566</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>44575</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44858</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>44655</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>44858</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44753</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>44810</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44753</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44580</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>44809</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>44575</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>44526</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44532</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>44482</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>44497</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>44657</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>44768</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>44575</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>44664</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>44664</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>44694</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>44482</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>44728</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>44679</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>44490</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>44728</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>44482</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>45758</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>44862</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>45007</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>45588</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>44664</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45098</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>44867</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>44879</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>44859</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>45330</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45720</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>45762</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44964</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>44707</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>45044</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45565</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>45701</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>44526</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>45789</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>45476</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>45789</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>45048</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>44664</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>44482</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>46003</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>44844</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>45561</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>44477</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>44831</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>46009</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>46007</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>46007</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>46007</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>45539</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>45191</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>44531</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>45503</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>45999</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>46025</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>45267</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>46030</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>44910</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>45790</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45903</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>44853</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>46036</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>45789</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>44623</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>45580</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>44609</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>44557</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>45526</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>45694</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>45694</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>45572</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>45656</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>44978</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>45727</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>45457</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>45274</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>46050</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>45632</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>45804</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>45804</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>45804</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>45033</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>45239</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>46052</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>46052</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45923</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>46052</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>46057</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>46057</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>45926</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>44600</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>45527</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>46064</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>45889</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>45937</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>46071</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>46071</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>45909</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>46071</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>46070</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45596</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>44753</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>45947</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>45097</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>45261</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>45804</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>45600</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45428</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>46090</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>45629</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>45219</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>45733</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>45677</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>46052</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>46092</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>44838</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>45966</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>44603</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>45715</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>45337</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>45523</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>46096</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>46099</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>46099</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>46099</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>46099</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>46099</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>46104</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>46106</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>45033</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>45548</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>45709</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>45979</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>45820</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>45979</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>45181</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45196</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44473</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>45617</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>45202</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>46120</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>46120</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44963</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>45993</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>44568</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>45181</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>44824</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>46007</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>44676</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>45358</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>45994</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>46070</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>46128</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>45999</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>46128</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>46127</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>45999</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>46001</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45183</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>44844</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>46127</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>44547</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>45831</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>44795</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>44575</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>45835</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>45225</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>45085</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>45223</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>45748</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45405</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>45040</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>45264</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>45764</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45631</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>45596</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>45825</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>45569</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45209</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>45520</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>45758</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>45429</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>45569</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>45565</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>44623</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>45393</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>44824</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>45877</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>45782</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45083</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>45679</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>45733</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45160</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>45868</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>45069</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         <v>45820</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>45527</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>45131</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>44477</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>45589</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>44872</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>45870</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>44907</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>46150</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>44979</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>46154</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>45733</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>45636</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>45083</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
         <v>46162</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>45044</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>46052</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>46052</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>45947</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>46167</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>45628</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>46167</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>45628</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>45596</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44941</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>46174</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>44502</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>44532</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>45215</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>45061</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>46177</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>46177</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>45021</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         <v>44941</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44941</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>45434</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24190,7 +24190,7 @@
         <v>44941</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>45511</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24336,7 +24336,7 @@
         <v>45701</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24409,7 +24409,7 @@
         <v>44761</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24482,7 +24482,7 @@
         <v>45099</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>45457</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>45677</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>46049</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>46209</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>44893</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>45553</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>46211</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>45001</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>44901</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>44907</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>44525</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>44789</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>46260</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>45369</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>46261</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>44525</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>44991</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25801,7 +25801,7 @@
         <v>44482</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
         <v>44482</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>45350</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26020,7 +26020,7 @@
         <v>45350</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>44980</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26166,7 +26166,7 @@
         <v>44676</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>46266</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         <v>45117</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>45744</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>46269</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>45609</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>45230</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26687,7 +26687,7 @@
         <v>46265</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>45554</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>46275</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>46279</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>46279</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27057,7 +27057,7 @@
         <v>44482</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>46281</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27203,7 +27203,7 @@
         <v>46281</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>45224</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44763</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>45008</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27495,7 +27495,7 @@
         <v>45607</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>44575</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>46287</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27714,7 +27714,7 @@
         <v>46287</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>46287</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>45596</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27933,7 +27933,7 @@
         <v>45631</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>45362</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>46265</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>45477</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>44531</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>46245</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>44869</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>46289</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>44827</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>45707</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>46290</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>45453</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>46290</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>45489</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>45139</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>46288</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45629</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>44753</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>44753</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>44839</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>44915</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>46294</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>45164</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>45055</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>44609</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29773,7 +29773,7 @@
         <v>45554</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>45155</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44875</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>44735</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>45323</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30143,7 +30143,7 @@
         <v>45448</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30216,7 +30216,7 @@
         <v>46255</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>45099</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30362,7 +30362,7 @@
         <v>45679</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30435,7 +30435,7 @@
         <v>45306</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30513,7 +30513,7 @@
         <v>45181</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>44966</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30659,7 +30659,7 @@
         <v>45632</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44950</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45764</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30878,7 +30878,7 @@
         <v>45385</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>45306</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>44900</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31097,7 +31097,7 @@
         <v>44508</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>44693</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>44594</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>44775</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>45377</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31462,7 +31462,7 @@
         <v>45638</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>45188</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>44496</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>45527</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>45489</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31827,7 +31827,7 @@
         <v>45618</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31900,7 +31900,7 @@
         <v>45741</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31973,7 +31973,7 @@
         <v>44438</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>45692</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>

--- a/Översikt ENKÖPING.xlsx
+++ b/Översikt ENKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44697</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45831</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>44910</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>46150</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46238</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45511</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>46269</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>44552</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>45104</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>44575</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>46233</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>45104</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44530</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>46255</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>46255</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>46265</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>44552</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44873</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>45226</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45215</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>45631</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>46170</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>45190</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>45762</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>45191</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>45825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>46070</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>44526</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>44910</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>45037</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>44722</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>45480</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>44735</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>44935</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>45697</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>45775</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>45994</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>46008</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>46272</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>46265</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>46279</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>46194</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45177</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>46203</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>44501</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>44497</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>44482</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44680</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>44622</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>44622</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>44851</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>44687</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>44819</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>44587</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>44566</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>44575</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>44858</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>44655</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>44858</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44753</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>44753</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>44810</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44580</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>44809</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44575</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44482</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>44679</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>44526</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>44768</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
         <v>44532</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>44482</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>44497</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>44575</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>44490</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>44728</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>44664</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>44664</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>44694</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>44728</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>44482</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>44657</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>44867</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>44482</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>44761</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>44496</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>45021</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>45183</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>45239</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>45085</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45188</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>44753</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>44753</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>45434</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>44872</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45720</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>45377</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>45181</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45733</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>45385</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>44879</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>44844</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>45350</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>45099</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>45323</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>45369</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>44941</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>44941</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>45330</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>45632</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>44824</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>45007</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>45457</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>44839</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>45139</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>45202</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>44508</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>44844</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>44893</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>45083</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>44915</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>44910</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>45358</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>45061</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>44568</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>44991</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>45629</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>45099</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45489</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>45001</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>45596</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>44980</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>45097</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>45306</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>45044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>44531</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>44979</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>45098</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>44664</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>44901</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>45405</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>45503</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>44482</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>44482</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>44941</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>44594</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>45230</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>44907</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>45477</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>45764</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>45429</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>45596</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>45733</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>44875</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>44853</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>45520</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>44531</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>45588</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>45733</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>45617</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>45903</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>44869</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>45428</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>45476</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>44525</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>45707</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14408,7 +14408,7 @@
         <v>45350</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14481,7 +14481,7 @@
         <v>45789</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>45448</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>45164</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>45527</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>44963</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>45362</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>45553</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>44978</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>45741</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>45181</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15211,7 +15211,7 @@
         <v>45618</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>45008</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>44609</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>45489</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>45789</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>45789</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>45758</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>45701</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         <v>45923</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>45790</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>44526</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>45926</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>44623</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>44664</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>45600</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>45694</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>44609</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>44547</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>45526</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>45656</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>45694</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>45580</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>45160</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>44603</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16968,7 +16968,7 @@
         <v>45727</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17041,7 +17041,7 @@
         <v>44557</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>44941</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>45048</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17260,7 +17260,7 @@
         <v>45523</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44964</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>45632</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>45457</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17552,7 +17552,7 @@
         <v>45804</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17625,7 +17625,7 @@
         <v>45804</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17698,7 +17698,7 @@
         <v>44795</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>44707</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>45554</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17917,7 +17917,7 @@
         <v>45554</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>44753</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18063,7 +18063,7 @@
         <v>44532</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>45527</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>45889</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>45453</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18355,7 +18355,7 @@
         <v>45677</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18428,7 +18428,7 @@
         <v>45909</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>45937</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
         <v>44789</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18652,7 +18652,7 @@
         <v>45629</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>45117</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>45638</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18871,7 +18871,7 @@
         <v>45820</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>44693</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>45947</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>45548</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19163,7 +19163,7 @@
         <v>45709</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>45561</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>44676</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45572</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>45083</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>45831</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>44763</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45804</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>45677</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>45679</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45835</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45966</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>45219</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>45225</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45636</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>45748</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45274</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>45631</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>45679</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>45764</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>45596</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45701</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>45758</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>45782</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45224</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>45267</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>45511</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>45055</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>45261</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>45868</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>44502</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>45870</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>45979</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>44907</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>44831</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>44950</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>45715</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>44735</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>45155</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>45596</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>45196</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>45744</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>46096</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>45762</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>46099</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>46099</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>46099</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>46099</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>45337</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>46099</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>44525</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>44623</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>45191</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23037,7 +23037,7 @@
         <v>45631</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>45979</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>45393</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23256,7 +23256,7 @@
         <v>45044</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>46106</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>44838</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23475,7 +23475,7 @@
         <v>44827</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>45069</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>45131</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>45993</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>45994</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>45539</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>46120</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>46120</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>46127</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>44676</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>44824</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>46127</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>44575</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>45999</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>45999</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
         <v>46007</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>46001</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>45040</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>46128</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>46128</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>46070</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>44862</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>45565</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>44859</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>44775</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>46003</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>46007</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>46007</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>44600</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>46007</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>44482</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>46009</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>45589</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>45999</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>45607</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>46025</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26103,7 +26103,7 @@
         <v>45264</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>46030</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26249,7 +26249,7 @@
         <v>45181</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26322,7 +26322,7 @@
         <v>45306</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26400,7 +26400,7 @@
         <v>46036</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>45033</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>45033</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26619,7 +26619,7 @@
         <v>45565</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>45820</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>45609</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>45569</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>45569</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>44575</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27057,7 +27057,7 @@
         <v>44966</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>45209</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27203,7 +27203,7 @@
         <v>44900</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>45527</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>45877</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>45825</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27495,7 +27495,7 @@
         <v>45223</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>46050</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>46052</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27714,7 +27714,7 @@
         <v>46052</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>46052</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>46057</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27933,7 +27933,7 @@
         <v>46057</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>46064</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>46150</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>46070</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>46071</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>46071</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>46154</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>46090</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>46052</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>46092</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>46162</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>46052</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>46052</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>45947</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>45628</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29028,7 +29028,7 @@
         <v>46167</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29101,7 +29101,7 @@
         <v>46167</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29174,7 +29174,7 @@
         <v>45628</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         <v>46174</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>45215</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29393,7 +29393,7 @@
         <v>46177</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>46177</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>46209</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>46049</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>46211</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>46266</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>46269</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29909,7 +29909,7 @@
         <v>46275</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29982,7 +29982,7 @@
         <v>46279</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>46279</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>46281</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>46281</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>46287</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30347,7 +30347,7 @@
         <v>46287</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>46287</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30493,7 +30493,7 @@
         <v>46265</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30566,7 +30566,7 @@
         <v>46245</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
         <v>46289</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30712,7 +30712,7 @@
         <v>46290</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>46290</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>46288</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>46294</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>46255</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>46304</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>46304</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>46260</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>46261</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>46304</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>46265</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>46303</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>44438</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31676,7 +31676,7 @@
         <v>45692</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>

--- a/Översikt ENKÖPING.xlsx
+++ b/Översikt ENKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44697</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45831</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>44910</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>46150</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46238</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45511</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>46269</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>44552</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>45104</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>44575</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>46233</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>45104</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44530</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>46255</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>46255</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>46265</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>44552</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44873</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>45226</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45215</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>45631</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>46170</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>45190</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>45762</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>45191</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>45825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>46070</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>44526</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>44910</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>45037</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>44722</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>45480</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>44735</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>44935</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>45697</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>45775</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>45994</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>46008</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>46272</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>46265</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>46279</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>46194</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45177</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>46203</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>44501</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>44497</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>44482</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44680</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>44622</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>44622</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>44851</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>44687</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>44819</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>44587</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>44566</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>44575</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>44858</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>44655</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>44858</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44753</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>44753</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>44810</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44580</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>44809</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44575</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44482</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>44679</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>44526</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>44768</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
         <v>44532</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>44482</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>44497</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>44575</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>44490</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>44728</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>44664</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>44664</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>44694</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>44728</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>44482</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>44657</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>44867</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>44482</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>44761</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>44496</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>45021</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>45183</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>45239</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>45085</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45188</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>44753</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>44753</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>45434</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>44872</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45720</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>45377</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>45181</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45733</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>45385</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>44879</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>44844</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>45350</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>45099</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>45323</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>45369</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>44941</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>44941</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>45330</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>45632</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>44824</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>45007</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>45457</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>44839</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>45139</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>45202</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>44508</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>44844</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>44893</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>45083</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>44915</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>44910</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>45358</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>45061</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>44568</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>44991</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>45629</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>45099</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45489</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>45001</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>45596</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>44980</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>45097</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>45306</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>45044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>44531</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>44979</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>45098</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>44664</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>44901</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>45405</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>45503</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>44482</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>44482</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>44941</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>44594</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>45230</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>44907</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>45477</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>45764</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>45429</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>45596</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>45733</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>44875</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>44853</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>45520</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>44531</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>45588</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>45733</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>45617</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>45903</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>44869</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>45428</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>45476</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>44525</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>45707</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14408,7 +14408,7 @@
         <v>45350</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14481,7 +14481,7 @@
         <v>45789</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>45448</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>45164</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>45527</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>44963</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>45362</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>45553</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>44978</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>45741</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>45181</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15211,7 +15211,7 @@
         <v>45618</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>45008</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>44609</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>45489</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>45789</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>45789</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>45758</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>45701</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         <v>45923</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>45790</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>44526</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>45926</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>44623</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>44664</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>45600</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>45694</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>44609</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>44547</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>45526</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>45656</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>45694</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>45580</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>45160</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>44603</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16968,7 +16968,7 @@
         <v>45727</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17041,7 +17041,7 @@
         <v>44557</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>44941</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>45048</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17260,7 +17260,7 @@
         <v>45523</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44964</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>45632</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>45457</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17552,7 +17552,7 @@
         <v>45804</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17625,7 +17625,7 @@
         <v>45804</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17698,7 +17698,7 @@
         <v>44795</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>44707</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>45554</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17917,7 +17917,7 @@
         <v>45554</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>44753</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18063,7 +18063,7 @@
         <v>44532</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>45527</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>45889</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>45453</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18355,7 +18355,7 @@
         <v>45677</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18428,7 +18428,7 @@
         <v>45909</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>45937</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
         <v>44789</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18652,7 +18652,7 @@
         <v>45629</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>45117</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>45638</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18871,7 +18871,7 @@
         <v>45820</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>44693</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>45947</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>45548</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19163,7 +19163,7 @@
         <v>45709</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>45561</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>44676</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45572</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>45083</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>45831</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>44763</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45804</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>45677</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>45679</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45835</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45966</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>45219</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>45225</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45636</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>45748</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45274</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>45631</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>45679</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>45764</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>45596</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45701</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>45758</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>45782</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45224</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>45267</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>45511</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>45055</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>45261</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>45868</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>44502</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>45870</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>45979</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>44907</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>44831</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>44950</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>45715</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>44735</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>45155</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>45596</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>45196</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>45744</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>46096</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>45762</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>46099</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>46099</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>46099</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>46099</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>45337</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>46099</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>44525</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>44623</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>45191</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23037,7 +23037,7 @@
         <v>45631</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>45979</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>45393</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23256,7 +23256,7 @@
         <v>45044</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>46106</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>44838</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23475,7 +23475,7 @@
         <v>44827</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>45069</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>45131</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>45993</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>45994</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>45539</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>46120</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>46120</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>46127</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>44676</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>44824</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>46127</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>44575</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>45999</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>45999</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
         <v>46007</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>46001</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>45040</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>46128</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>46128</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>46070</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>44862</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>45565</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>44859</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>44775</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>46003</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>46007</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>46007</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>44600</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>46007</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>44482</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>46009</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>45589</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>45999</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>45607</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>46025</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26103,7 +26103,7 @@
         <v>45264</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>46030</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26249,7 +26249,7 @@
         <v>45181</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26322,7 +26322,7 @@
         <v>45306</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26400,7 +26400,7 @@
         <v>46036</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>45033</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>45033</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26619,7 +26619,7 @@
         <v>45565</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>45820</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>45609</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>45569</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>45569</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>44575</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27057,7 +27057,7 @@
         <v>44966</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>45209</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27203,7 +27203,7 @@
         <v>44900</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>45527</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>45877</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>45825</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27495,7 +27495,7 @@
         <v>45223</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>46050</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>46052</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27714,7 +27714,7 @@
         <v>46052</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>46052</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>46057</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27933,7 +27933,7 @@
         <v>46057</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>46064</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>46150</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>46070</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>46071</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>46071</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>46154</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>46090</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>46052</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>46092</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>46162</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>46052</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>46052</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>45947</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>45628</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29028,7 +29028,7 @@
         <v>46167</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29101,7 +29101,7 @@
         <v>46167</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29174,7 +29174,7 @@
         <v>45628</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         <v>46174</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>45215</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29393,7 +29393,7 @@
         <v>46177</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>46177</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>46209</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>46049</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>46211</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>46266</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>46269</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29909,7 +29909,7 @@
         <v>46275</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29982,7 +29982,7 @@
         <v>46279</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>46279</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>46281</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>46281</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>46287</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30347,7 +30347,7 @@
         <v>46287</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>46287</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30493,7 +30493,7 @@
         <v>46265</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30566,7 +30566,7 @@
         <v>46245</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
         <v>46289</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30712,7 +30712,7 @@
         <v>46290</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>46290</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>46288</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>46294</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>46255</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>46304</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>46304</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>46260</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>46261</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>46304</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>46265</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>46303</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>44438</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31676,7 +31676,7 @@
         <v>45692</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>

--- a/Översikt ENKÖPING.xlsx
+++ b/Översikt ENKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44697</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45831</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>44910</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>46150</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46238</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45511</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>46269</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>44552</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>44575</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>46233</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>45104</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>45104</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44530</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>46255</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>46255</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>46265</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>44552</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44873</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>45215</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45226</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>45631</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>46170</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>45825</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>45191</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>46070</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>45190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45762</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>44526</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>45697</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>44935</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>45994</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>45480</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>46008</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>44735</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>44910</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>46272</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>46279</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>44722</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>45775</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>46194</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>45037</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>46265</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45177</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>46203</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>44501</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>44497</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>44622</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44622</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>44680</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>44851</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>44687</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>44819</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>44587</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>44566</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>44575</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>44858</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>44655</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>44858</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>44753</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44810</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>44753</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>44580</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44809</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>44575</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44526</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44532</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>44497</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>44657</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>44768</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
         <v>44575</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>44664</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>44664</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>44694</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>44728</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>44679</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>44490</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>44728</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>45007</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>44867</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>45758</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>44862</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>45588</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>45098</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>44879</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>44664</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>44859</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>45330</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>45720</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>45565</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45762</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>44707</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>45044</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>44964</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>45476</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>44664</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>44831</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>45561</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>44844</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>45539</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45191</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>45503</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>45048</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>45267</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>44910</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>44623</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>44978</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>45572</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         <v>45274</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>45033</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>45239</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>44600</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>45596</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>44753</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         <v>45600</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>45097</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>45261</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>45733</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>45428</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10972,7 +10972,7 @@
         <v>45629</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>45219</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>44838</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>44603</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>45715</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>45337</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>45523</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>45033</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>45181</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45264</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>45825</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>45196</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>45617</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>45202</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>45569</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>44963</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>44568</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>45181</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>44531</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>45569</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>45358</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>45183</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>44844</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>45061</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>44547</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>45565</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>45877</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>44795</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>44575</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>45225</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>45085</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>44853</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>45820</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>45789</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>45223</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45405</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>45040</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>45923</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>45209</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>45520</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>45429</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>45926</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>45889</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>45937</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>46150</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>45909</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>44623</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>45393</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>44824</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>46154</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45947</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>45083</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>45804</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>45679</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>45733</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>45677</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>45160</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45069</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>45966</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>45527</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>45131</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>45589</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>46162</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>44872</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>46052</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>46052</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>45979</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>44907</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>44979</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>45947</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>46167</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>45733</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>45628</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>45979</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>45636</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>46167</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>45083</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>45628</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>45993</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>45044</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>45994</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>45999</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>45999</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>46001</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>46003</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>46009</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>46007</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>46007</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>44941</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>46007</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>46174</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>44502</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44532</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>45999</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>46025</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>45021</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>44941</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>44941</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>46030</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>45434</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>46036</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>45215</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>46177</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>46177</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>44941</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>45511</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>45701</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>46050</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>46052</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>46052</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>46052</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>46057</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>44761</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>46057</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>45099</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>45457</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>46064</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>46071</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>46071</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>46070</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45677</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>46090</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>44893</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>45553</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>46052</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>46092</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>45001</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>44901</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>44907</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>44525</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>46096</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>46099</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>44789</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>46099</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>46099</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>46099</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>46099</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>45369</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>44525</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>46106</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>44991</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>45350</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>45350</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         <v>46120</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>44980</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>46120</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>44676</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>44824</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>46007</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>44676</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>46070</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>46128</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>45117</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>45744</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>46128</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>46127</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>46127</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>45609</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>45230</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>45554</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>45224</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>44763</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45008</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>46049</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>46209</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>45607</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>44575</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>46211</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45596</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>45631</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45362</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>45477</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>44531</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>44869</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>44827</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>45707</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
         <v>45453</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         <v>46275</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>45489</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24049,7 +24049,7 @@
         <v>45139</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>46279</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>46279</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>45629</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>44753</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>44753</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24487,7 +24487,7 @@
         <v>44839</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24560,7 +24560,7 @@
         <v>44915</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         <v>45164</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24706,7 +24706,7 @@
         <v>45055</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>44609</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>46281</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>45554</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25003,7 +25003,7 @@
         <v>46281</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         <v>45155</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44875</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>44735</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>45323</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>45448</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>46287</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>46287</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>46287</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>45099</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>45679</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>45306</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>45181</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>44966</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>46245</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>46289</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>45632</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26254,7 +26254,7 @@
         <v>46290</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26332,7 +26332,7 @@
         <v>44950</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>45764</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         <v>46290</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>46288</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45385</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>45306</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>44900</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>46294</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>44508</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>44693</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>44594</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>44775</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>45377</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>46255</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45638</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>45188</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>44496</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45527</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>45489</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>45618</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>45741</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>45701</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>44526</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>46303</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
         <v>45789</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>45789</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         <v>46260</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>45790</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>46261</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28454,7 +28454,7 @@
         <v>45580</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>44609</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>46307</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44557</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28746,7 +28746,7 @@
         <v>46304</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28819,7 +28819,7 @@
         <v>45526</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>45694</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>45694</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>45656</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45727</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>45457</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>45903</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>46304</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>46304</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>45632</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>46265</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>45804</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>45804</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45527</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>46266</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>46265</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45548</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>45709</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
         <v>46269</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30216,7 +30216,7 @@
         <v>45820</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>45831</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30362,7 +30362,7 @@
         <v>45835</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30435,7 +30435,7 @@
         <v>45748</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30508,7 +30508,7 @@
         <v>45764</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>45631</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>45596</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>45758</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>45782</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>45868</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30946,7 +30946,7 @@
         <v>45870</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>45596</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>44438</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>45692</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>

--- a/Översikt ENKÖPING.xlsx
+++ b/Översikt ENKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44697</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45831</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>44910</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>46150</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46238</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45511</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>46269</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>44552</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>44575</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>46233</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>45104</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>45104</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44530</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>46255</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>46255</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>46265</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>44552</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44873</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>45215</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45226</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>45631</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>46170</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>45825</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>45191</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>46070</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>45190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45762</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>44526</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>45697</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>44935</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>45994</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>45480</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>46008</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>44735</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>44910</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>46272</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>46279</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>44722</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>45775</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>46194</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>45037</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>46265</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45177</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>46203</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>44501</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>44497</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>44622</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44622</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>44680</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>44851</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>44687</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>44819</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>44587</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>44566</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>44575</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>44858</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>44655</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>44858</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>44753</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44810</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>44753</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>44580</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44809</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>44575</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44526</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44532</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>44497</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>44657</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>44768</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
         <v>44575</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>44664</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>44664</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>44694</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>44728</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>44679</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>44490</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>44728</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>45007</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>44867</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>45758</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>44862</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>45588</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>45098</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>44879</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>44664</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>44859</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>45330</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>45720</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>45565</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45762</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>44707</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>45044</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>44964</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>45476</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>44664</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>44831</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>45561</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>44844</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>45539</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45191</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>45503</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>45048</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>45267</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>44910</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>44623</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>44978</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>45572</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         <v>45274</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>45033</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>45239</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>44600</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>45596</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>44753</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         <v>45600</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>45097</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>45261</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>45733</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>45428</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10972,7 +10972,7 @@
         <v>45629</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>45219</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>44838</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>44603</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>45715</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>45337</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>45523</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>45033</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>45181</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45264</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>45825</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>45196</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>45617</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>45202</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>45569</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>44963</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>44568</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>45181</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>44531</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>45569</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>45358</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>45183</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>44844</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>45061</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>44547</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>45565</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>45877</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>44795</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>44575</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>45225</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>45085</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>44853</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>45820</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>45789</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>45223</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45405</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>45040</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>45923</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>45209</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>45520</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>45429</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>45926</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>45889</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>45937</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>46150</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>45909</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>44623</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>45393</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>44824</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>46154</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45947</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>45083</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>45804</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>45679</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>45733</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>45677</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>45160</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45069</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>45966</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>45527</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>45131</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>45589</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>46162</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>44872</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>46052</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>46052</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>45979</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>44907</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>44979</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>45947</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>46167</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>45733</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>45628</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>45979</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>45636</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>46167</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>45083</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>45628</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>45993</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>45044</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>45994</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>45999</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>45999</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>46001</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>46003</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>46009</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>46007</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>46007</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>44941</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>46007</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>46174</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>44502</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44532</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>45999</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>46025</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>45021</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>44941</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>44941</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>46030</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>45434</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>46036</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>45215</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>46177</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>46177</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>44941</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>45511</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>45701</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>46050</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>46052</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>46052</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>46052</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>46057</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>44761</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>46057</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>45099</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>45457</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>46064</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>46071</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>46071</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>46070</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45677</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>46090</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>44893</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>45553</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>46052</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>46092</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>45001</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>44901</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>44907</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>44525</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>46096</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>46099</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>44789</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>46099</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>46099</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>46099</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>46099</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>45369</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>44525</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>46106</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>44991</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>45350</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>45350</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         <v>46120</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>44980</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>46120</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>44676</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>44824</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>46007</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>44676</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>46070</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>46128</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>45117</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>45744</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>46128</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>46127</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>46127</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>45609</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>45230</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>45554</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>45224</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>44763</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45008</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>46049</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>46209</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>45607</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>44575</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>46211</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45596</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>45631</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45362</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>45477</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>44531</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>44869</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>44827</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>45707</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
         <v>45453</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         <v>46275</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>45489</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24049,7 +24049,7 @@
         <v>45139</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>46279</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>46279</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>45629</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>44753</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>44753</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24487,7 +24487,7 @@
         <v>44839</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24560,7 +24560,7 @@
         <v>44915</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         <v>45164</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24706,7 +24706,7 @@
         <v>45055</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>44609</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>46281</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>45554</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25003,7 +25003,7 @@
         <v>46281</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         <v>45155</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44875</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>44735</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>45323</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>45448</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>46287</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>46287</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>46287</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>45099</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>45679</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>45306</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>45181</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>44966</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>46245</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>46289</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>45632</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26254,7 +26254,7 @@
         <v>46290</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26332,7 +26332,7 @@
         <v>44950</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>45764</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         <v>46290</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>46288</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45385</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>45306</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>44900</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>46294</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>44508</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>44693</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>44594</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>44775</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>45377</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>46255</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45638</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>45188</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>44496</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45527</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>45489</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>45618</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>45741</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>45701</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>44526</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>46303</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
         <v>45789</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>45789</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         <v>46260</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>45790</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>46261</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28454,7 +28454,7 @@
         <v>45580</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>44609</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>46307</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44557</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28746,7 +28746,7 @@
         <v>46304</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28819,7 +28819,7 @@
         <v>45526</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>45694</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>45694</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>45656</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45727</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>45457</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>45903</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>46304</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>46304</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>45632</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>46265</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>45804</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>45804</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45527</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>46266</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>46265</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45548</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>45709</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
         <v>46269</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30216,7 +30216,7 @@
         <v>45820</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>45831</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30362,7 +30362,7 @@
         <v>45835</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30435,7 +30435,7 @@
         <v>45748</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30508,7 +30508,7 @@
         <v>45764</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>45631</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>45596</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>45758</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>45782</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>45868</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30946,7 +30946,7 @@
         <v>45870</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>45596</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>44438</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>45692</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>

--- a/Översikt ENKÖPING.xlsx
+++ b/Översikt ENKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44697</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45831</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>44910</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>46150</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46279</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
@@ -1161,19 +1161,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
@@ -1182,6 +1182,7 @@
 Rynkskinn
 Talltita
 Ullticka
+Vaddporing
 Bronshjon
 Granbarkgnagare
 Mindre märgborre
@@ -1249,7 +1250,7 @@
         <v>46238</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1365,7 +1366,7 @@
         <v>45511</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1476,7 +1477,7 @@
         <v>46269</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1591,7 +1592,7 @@
         <v>46112</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1706,7 +1707,7 @@
         <v>44552</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1820,7 +1821,7 @@
         <v>44575</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1929,7 +1930,7 @@
         <v>46233</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2038,7 +2039,7 @@
         <v>45104</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2147,7 +2148,7 @@
         <v>45104</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2256,7 +2257,7 @@
         <v>44530</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2364,7 +2365,7 @@
         <v>46281</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2480,7 +2481,7 @@
         <v>46255</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2588,7 +2589,7 @@
         <v>46255</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2696,7 +2697,7 @@
         <v>46265</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2813,7 +2814,7 @@
         <v>44552</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2925,7 +2926,7 @@
         <v>44873</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3032,7 +3033,7 @@
         <v>45226</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3139,7 +3140,7 @@
         <v>45215</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3246,7 +3247,7 @@
         <v>45631</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3353,7 +3354,7 @@
         <v>46170</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3460,7 +3461,7 @@
         <v>45190</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3566,7 +3567,7 @@
         <v>45762</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3672,7 +3673,7 @@
         <v>46070</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3778,7 +3779,7 @@
         <v>45825</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3884,7 +3885,7 @@
         <v>45191</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3990,7 +3991,7 @@
         <v>44526</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4095,7 +4096,7 @@
         <v>45994</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4204,7 +4205,7 @@
         <v>44910</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4309,7 +4310,7 @@
         <v>46008</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4414,7 +4415,7 @@
         <v>46279</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4519,7 +4520,7 @@
         <v>45037</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4628,7 +4629,7 @@
         <v>46265</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4742,7 +4743,7 @@
         <v>46194</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4851,7 +4852,7 @@
         <v>46272</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4956,7 +4957,7 @@
         <v>44722</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5061,7 +5062,7 @@
         <v>45480</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5166,7 +5167,7 @@
         <v>44935</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5271,7 +5272,7 @@
         <v>45697</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5376,7 +5377,7 @@
         <v>45775</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5481,7 +5482,7 @@
         <v>44735</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5586,7 +5587,7 @@
         <v>45177</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5691,7 +5692,7 @@
         <v>46203</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5796,7 +5797,7 @@
         <v>44501</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5869,7 +5870,7 @@
         <v>44497</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5942,7 +5943,7 @@
         <v>44622</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6015,7 +6016,7 @@
         <v>44680</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6088,7 +6089,7 @@
         <v>44622</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6161,7 +6162,7 @@
         <v>44851</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6234,7 +6235,7 @@
         <v>44687</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6307,7 +6308,7 @@
         <v>44819</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6380,7 +6381,7 @@
         <v>44587</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6453,7 +6454,7 @@
         <v>44566</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6531,7 +6532,7 @@
         <v>44575</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6604,7 +6605,7 @@
         <v>44858</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6677,7 +6678,7 @@
         <v>44655</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6750,7 +6751,7 @@
         <v>44858</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6823,7 +6824,7 @@
         <v>44753</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6896,7 +6897,7 @@
         <v>44810</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6969,7 +6970,7 @@
         <v>44753</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7042,7 +7043,7 @@
         <v>44580</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7115,7 +7116,7 @@
         <v>44809</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7188,7 +7189,7 @@
         <v>44575</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7261,7 +7262,7 @@
         <v>44526</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7334,7 +7335,7 @@
         <v>44532</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7407,7 +7408,7 @@
         <v>44497</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7480,7 +7481,7 @@
         <v>44657</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7553,7 +7554,7 @@
         <v>44768</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7631,7 +7632,7 @@
         <v>44575</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7704,7 +7705,7 @@
         <v>44664</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7777,7 +7778,7 @@
         <v>44664</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7850,7 +7851,7 @@
         <v>44694</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7923,7 +7924,7 @@
         <v>44728</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7996,7 +7997,7 @@
         <v>44679</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8069,7 +8070,7 @@
         <v>44728</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8142,7 +8143,7 @@
         <v>45720</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8215,7 +8216,7 @@
         <v>45181</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8288,7 +8289,7 @@
         <v>45733</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8361,7 +8362,7 @@
         <v>45323</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8434,7 +8435,7 @@
         <v>45330</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8507,7 +8508,7 @@
         <v>44600</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8580,7 +8581,7 @@
         <v>44531</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8653,7 +8654,7 @@
         <v>45083</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8726,7 +8727,7 @@
         <v>45589</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8799,7 +8800,7 @@
         <v>44867</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8872,7 +8873,7 @@
         <v>45607</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8945,7 +8946,7 @@
         <v>44853</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9018,7 +9019,7 @@
         <v>44761</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9091,7 +9092,7 @@
         <v>45789</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9164,7 +9165,7 @@
         <v>46162</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9237,7 +9238,7 @@
         <v>46052</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9310,7 +9311,7 @@
         <v>46052</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9383,7 +9384,7 @@
         <v>45181</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9456,7 +9457,7 @@
         <v>45947</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9529,7 +9530,7 @@
         <v>45306</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9607,7 +9608,7 @@
         <v>45628</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9680,7 +9681,7 @@
         <v>45033</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9753,7 +9754,7 @@
         <v>45033</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9826,7 +9827,7 @@
         <v>46167</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9899,7 +9900,7 @@
         <v>46167</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9972,7 +9973,7 @@
         <v>45923</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10045,7 +10046,7 @@
         <v>45926</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10118,7 +10119,7 @@
         <v>45609</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10191,7 +10192,7 @@
         <v>45628</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10264,7 +10265,7 @@
         <v>45434</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10337,7 +10338,7 @@
         <v>44575</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10410,7 +10411,7 @@
         <v>44966</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10483,7 +10484,7 @@
         <v>45209</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10556,7 +10557,7 @@
         <v>44900</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10629,7 +10630,7 @@
         <v>45527</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10702,7 +10703,7 @@
         <v>45223</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10775,7 +10776,7 @@
         <v>44872</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10848,7 +10849,7 @@
         <v>45889</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10921,7 +10922,7 @@
         <v>45909</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10994,7 +10995,7 @@
         <v>46174</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11067,7 +11068,7 @@
         <v>44496</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11140,7 +11141,7 @@
         <v>45937</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11213,7 +11214,7 @@
         <v>45021</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11286,7 +11287,7 @@
         <v>45183</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11359,7 +11360,7 @@
         <v>45385</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11432,7 +11433,7 @@
         <v>45239</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11505,7 +11506,7 @@
         <v>45215</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11578,7 +11579,7 @@
         <v>46177</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11651,7 +11652,7 @@
         <v>46177</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11724,7 +11725,7 @@
         <v>44824</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11797,7 +11798,7 @@
         <v>45457</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11870,7 +11871,7 @@
         <v>44839</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11943,7 +11944,7 @@
         <v>45202</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12016,7 +12017,7 @@
         <v>44844</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12089,7 +12090,7 @@
         <v>44893</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12162,7 +12163,7 @@
         <v>45377</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12235,7 +12236,7 @@
         <v>45947</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12308,7 +12309,7 @@
         <v>44844</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12381,7 +12382,7 @@
         <v>45804</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12454,7 +12455,7 @@
         <v>45632</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12527,7 +12528,7 @@
         <v>44910</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12605,7 +12606,7 @@
         <v>45677</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12678,7 +12679,7 @@
         <v>45139</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12751,7 +12752,7 @@
         <v>45966</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12824,7 +12825,7 @@
         <v>45629</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12897,7 +12898,7 @@
         <v>45001</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12970,7 +12971,7 @@
         <v>45596</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13043,7 +13044,7 @@
         <v>44980</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13116,7 +13117,7 @@
         <v>45097</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13189,7 +13190,7 @@
         <v>45044</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13262,7 +13263,7 @@
         <v>44979</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13335,7 +13336,7 @@
         <v>45098</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13408,7 +13409,7 @@
         <v>45979</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13481,7 +13482,7 @@
         <v>44664</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13554,7 +13555,7 @@
         <v>45230</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13632,7 +13633,7 @@
         <v>44907</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13705,7 +13706,7 @@
         <v>45489</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13778,7 +13779,7 @@
         <v>45979</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13851,7 +13852,7 @@
         <v>45596</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13924,7 +13925,7 @@
         <v>46209</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13997,7 +13998,7 @@
         <v>45733</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14070,7 +14071,7 @@
         <v>46049</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14143,7 +14144,7 @@
         <v>46211</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14216,7 +14217,7 @@
         <v>44875</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14289,7 +14290,7 @@
         <v>45993</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14362,7 +14363,7 @@
         <v>45306</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14435,7 +14436,7 @@
         <v>45994</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14508,7 +14509,7 @@
         <v>45588</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14581,7 +14582,7 @@
         <v>45733</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14654,7 +14655,7 @@
         <v>45617</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14727,7 +14728,7 @@
         <v>44869</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14800,7 +14801,7 @@
         <v>45999</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14873,7 +14874,7 @@
         <v>45707</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14946,7 +14947,7 @@
         <v>45350</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15019,7 +15020,7 @@
         <v>45999</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15092,7 +15093,7 @@
         <v>46001</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15165,7 +15166,7 @@
         <v>45527</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15238,7 +15239,7 @@
         <v>46003</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15311,7 +15312,7 @@
         <v>46007</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15384,7 +15385,7 @@
         <v>46007</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15457,7 +15458,7 @@
         <v>46007</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15530,7 +15531,7 @@
         <v>46009</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15603,7 +15604,7 @@
         <v>45741</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15676,7 +15677,7 @@
         <v>45618</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15749,7 +15750,7 @@
         <v>46279</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15822,7 +15823,7 @@
         <v>45489</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15895,7 +15896,7 @@
         <v>45999</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15968,7 +15969,7 @@
         <v>45789</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16041,7 +16042,7 @@
         <v>45789</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16114,7 +16115,7 @@
         <v>45701</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16187,7 +16188,7 @@
         <v>46281</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16260,7 +16261,7 @@
         <v>46025</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16333,7 +16334,7 @@
         <v>45790</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16406,7 +16407,7 @@
         <v>44526</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16479,7 +16480,7 @@
         <v>46030</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16552,7 +16553,7 @@
         <v>46036</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16625,7 +16626,7 @@
         <v>45694</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16698,7 +16699,7 @@
         <v>44609</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16771,7 +16772,7 @@
         <v>45526</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16844,7 +16845,7 @@
         <v>45656</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16917,7 +16918,7 @@
         <v>45694</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16990,7 +16991,7 @@
         <v>45580</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17063,7 +17064,7 @@
         <v>45727</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17136,7 +17137,7 @@
         <v>44557</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17209,7 +17210,7 @@
         <v>46287</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17282,7 +17283,7 @@
         <v>46287</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17355,7 +17356,7 @@
         <v>46287</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17428,7 +17429,7 @@
         <v>45632</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17501,7 +17502,7 @@
         <v>46245</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17574,7 +17575,7 @@
         <v>45457</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17647,7 +17648,7 @@
         <v>46050</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17720,7 +17721,7 @@
         <v>46289</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17793,7 +17794,7 @@
         <v>45804</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17866,7 +17867,7 @@
         <v>46052</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17939,7 +17940,7 @@
         <v>46052</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18012,7 +18013,7 @@
         <v>46052</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18085,7 +18086,7 @@
         <v>45804</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18158,7 +18159,7 @@
         <v>45503</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18231,7 +18232,7 @@
         <v>46290</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18309,7 +18310,7 @@
         <v>45527</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18382,7 +18383,7 @@
         <v>46057</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18455,7 +18456,7 @@
         <v>46290</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18533,7 +18534,7 @@
         <v>46288</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18606,7 +18607,7 @@
         <v>46057</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18679,7 +18680,7 @@
         <v>46294</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18752,7 +18753,7 @@
         <v>46064</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18825,7 +18826,7 @@
         <v>44941</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18898,7 +18899,7 @@
         <v>46070</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18971,7 +18972,7 @@
         <v>45820</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19044,7 +19045,7 @@
         <v>46071</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19117,7 +19118,7 @@
         <v>45548</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19190,7 +19191,7 @@
         <v>45709</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19263,7 +19264,7 @@
         <v>46071</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19336,7 +19337,7 @@
         <v>45831</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19409,7 +19410,7 @@
         <v>45477</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19482,7 +19483,7 @@
         <v>45835</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19555,7 +19556,7 @@
         <v>46090</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19628,7 +19629,7 @@
         <v>46052</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19701,7 +19702,7 @@
         <v>46092</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19774,7 +19775,7 @@
         <v>46096</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19847,7 +19848,7 @@
         <v>46099</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19920,7 +19921,7 @@
         <v>46099</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19993,7 +19994,7 @@
         <v>46099</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20066,7 +20067,7 @@
         <v>46099</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20139,7 +20140,7 @@
         <v>46099</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20212,7 +20213,7 @@
         <v>45748</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20285,7 +20286,7 @@
         <v>45631</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20358,7 +20359,7 @@
         <v>46255</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20431,7 +20432,7 @@
         <v>45764</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20504,7 +20505,7 @@
         <v>45596</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20577,7 +20578,7 @@
         <v>45758</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20650,7 +20651,7 @@
         <v>46106</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20723,7 +20724,7 @@
         <v>45782</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20796,7 +20797,7 @@
         <v>46304</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20869,7 +20870,7 @@
         <v>46304</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20942,7 +20943,7 @@
         <v>45868</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21015,7 +21016,7 @@
         <v>46260</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21088,7 +21089,7 @@
         <v>46120</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21161,7 +21162,7 @@
         <v>45870</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21234,7 +21235,7 @@
         <v>46261</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21307,7 +21308,7 @@
         <v>46304</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21380,7 +21381,7 @@
         <v>46120</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21453,7 +21454,7 @@
         <v>44531</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21526,7 +21527,7 @@
         <v>46127</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21599,7 +21600,7 @@
         <v>46303</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21672,7 +21673,7 @@
         <v>44676</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21745,7 +21746,7 @@
         <v>44824</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21818,7 +21819,7 @@
         <v>46127</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21891,7 +21892,7 @@
         <v>46007</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21964,7 +21965,7 @@
         <v>46128</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22037,7 +22038,7 @@
         <v>45903</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22110,7 +22111,7 @@
         <v>46128</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22183,7 +22184,7 @@
         <v>45596</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22256,7 +22257,7 @@
         <v>46070</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22329,7 +22330,7 @@
         <v>46265</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22402,7 +22403,7 @@
         <v>45476</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22475,7 +22476,7 @@
         <v>45061</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22548,7 +22549,7 @@
         <v>45448</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22621,7 +22622,7 @@
         <v>45362</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22694,7 +22695,7 @@
         <v>46307</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22767,7 +22768,7 @@
         <v>46266</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22840,7 +22841,7 @@
         <v>45181</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22913,7 +22914,7 @@
         <v>46265</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22991,7 +22992,7 @@
         <v>45008</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23064,7 +23065,7 @@
         <v>45264</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23137,7 +23138,7 @@
         <v>46269</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23215,7 +23216,7 @@
         <v>44623</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23288,7 +23289,7 @@
         <v>45565</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23361,7 +23362,7 @@
         <v>45820</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23434,7 +23435,7 @@
         <v>45569</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23507,7 +23508,7 @@
         <v>45569</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23580,7 +23581,7 @@
         <v>45877</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23653,7 +23654,7 @@
         <v>45825</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23726,7 +23727,7 @@
         <v>44941</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23799,7 +23800,7 @@
         <v>46275</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23872,7 +23873,7 @@
         <v>45523</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23945,7 +23946,7 @@
         <v>44964</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24018,7 +24019,7 @@
         <v>44707</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24091,7 +24092,7 @@
         <v>44753</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24164,7 +24165,7 @@
         <v>46150</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24237,7 +24238,7 @@
         <v>46154</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24310,7 +24311,7 @@
         <v>45629</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24383,7 +24384,7 @@
         <v>45083</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24456,7 +24457,7 @@
         <v>45636</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24529,7 +24530,7 @@
         <v>45679</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24602,7 +24603,7 @@
         <v>45701</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24675,7 +24676,7 @@
         <v>45224</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24748,7 +24749,7 @@
         <v>45511</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24821,7 +24822,7 @@
         <v>45055</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24894,7 +24895,7 @@
         <v>44502</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24967,7 +24968,7 @@
         <v>44907</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25040,7 +25041,7 @@
         <v>44831</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25113,7 +25114,7 @@
         <v>45715</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25186,7 +25187,7 @@
         <v>45155</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25259,7 +25260,7 @@
         <v>45196</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25332,7 +25333,7 @@
         <v>45744</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25405,7 +25406,7 @@
         <v>45762</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25478,7 +25479,7 @@
         <v>45337</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25551,7 +25552,7 @@
         <v>44525</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25624,7 +25625,7 @@
         <v>44838</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25697,7 +25698,7 @@
         <v>44827</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25770,7 +25771,7 @@
         <v>45069</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25843,7 +25844,7 @@
         <v>45085</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25916,7 +25917,7 @@
         <v>45188</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25989,7 +25990,7 @@
         <v>44753</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26062,7 +26063,7 @@
         <v>44753</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26135,7 +26136,7 @@
         <v>44879</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26208,7 +26209,7 @@
         <v>45350</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26281,7 +26282,7 @@
         <v>45099</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26354,7 +26355,7 @@
         <v>45369</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26427,7 +26428,7 @@
         <v>44941</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26500,7 +26501,7 @@
         <v>44941</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26573,7 +26574,7 @@
         <v>45007</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26646,7 +26647,7 @@
         <v>44508</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26719,7 +26720,7 @@
         <v>44915</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26792,7 +26793,7 @@
         <v>45358</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26865,7 +26866,7 @@
         <v>44568</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26938,7 +26939,7 @@
         <v>44991</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27011,7 +27012,7 @@
         <v>45099</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27084,7 +27085,7 @@
         <v>44901</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27157,7 +27158,7 @@
         <v>45405</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27230,7 +27231,7 @@
         <v>44594</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27303,7 +27304,7 @@
         <v>45764</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27376,7 +27377,7 @@
         <v>45429</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27449,7 +27450,7 @@
         <v>45520</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27522,7 +27523,7 @@
         <v>45428</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27595,7 +27596,7 @@
         <v>44525</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27668,7 +27669,7 @@
         <v>45164</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27741,7 +27742,7 @@
         <v>44963</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27814,7 +27815,7 @@
         <v>45553</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27887,7 +27888,7 @@
         <v>44978</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27960,7 +27961,7 @@
         <v>44609</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28038,7 +28039,7 @@
         <v>45758</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28111,7 +28112,7 @@
         <v>44664</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28184,7 +28185,7 @@
         <v>45600</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28257,7 +28258,7 @@
         <v>44547</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28330,7 +28331,7 @@
         <v>45160</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28403,7 +28404,7 @@
         <v>44603</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28476,7 +28477,7 @@
         <v>45048</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28549,7 +28550,7 @@
         <v>44795</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28622,7 +28623,7 @@
         <v>45554</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28695,7 +28696,7 @@
         <v>45554</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28768,7 +28769,7 @@
         <v>44532</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28841,7 +28842,7 @@
         <v>45453</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28914,7 +28915,7 @@
         <v>45677</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28987,7 +28988,7 @@
         <v>44789</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29065,7 +29066,7 @@
         <v>45117</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29138,7 +29139,7 @@
         <v>45638</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29211,7 +29212,7 @@
         <v>44693</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29284,7 +29285,7 @@
         <v>45561</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29357,7 +29358,7 @@
         <v>44676</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29430,7 +29431,7 @@
         <v>45572</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29503,7 +29504,7 @@
         <v>44763</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29576,7 +29577,7 @@
         <v>45679</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29649,7 +29650,7 @@
         <v>45219</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29722,7 +29723,7 @@
         <v>45225</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29795,7 +29796,7 @@
         <v>45274</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29868,7 +29869,7 @@
         <v>45267</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29941,7 +29942,7 @@
         <v>45261</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30014,7 +30015,7 @@
         <v>44950</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30087,7 +30088,7 @@
         <v>44735</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30165,7 +30166,7 @@
         <v>44623</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30238,7 +30239,7 @@
         <v>45191</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30311,7 +30312,7 @@
         <v>45631</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30384,7 +30385,7 @@
         <v>45393</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30457,7 +30458,7 @@
         <v>45044</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30530,7 +30531,7 @@
         <v>45131</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30603,7 +30604,7 @@
         <v>45539</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30676,7 +30677,7 @@
         <v>44575</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30749,7 +30750,7 @@
         <v>45040</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30822,7 +30823,7 @@
         <v>44862</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30895,7 +30896,7 @@
         <v>45565</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30968,7 +30969,7 @@
         <v>44859</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31041,7 +31042,7 @@
         <v>44775</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31114,7 +31115,7 @@
         <v>44438</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31187,7 +31188,7 @@
         <v>45692</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
